--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,50 +480,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>coach_home</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>coach_away</t>
+          <t>season</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_country</t>
+          <t>country</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
@@ -532,86 +512,61 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AszX60rp</t>
+          <t>hQiNHHd2</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Mendoza R.
- (Usa)</t>
-        </is>
-      </c>
+        <v>45528.8125</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Stadium
- (Atlanta, GA)</t>
+          <t>Allianz Field
+ (Saint Paul, MN)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71000</v>
+        <v>19400</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Atlanta Utd</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>l6eEjGlO</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>valentino rob</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>nancy wilfried</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>167</v>
       </c>
-      <c r="P2" t="n">
+      <c r="L2" t="n">
         <v>1671</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
+      <c r="N2" t="n">
         <v>2024</v>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -620,18 +575,13 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jix3jCxF</t>
+          <t>C6QBlj7R</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Villarreal A.
- (Usa)</t>
-        </is>
-      </c>
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Saputo Stadium
@@ -654,52 +604,32 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Toronto FC</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>K4FYmLD9</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>courtois laurent</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>herdman john</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>167</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>1671</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
+      <c r="N3" t="n">
         <v>2024</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -708,212 +638,157 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h6Py6Kcj</t>
+          <t>dbI3Q902</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>De Oliveira M.
- (Usa)</t>
-        </is>
-      </c>
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>Bank of America Stadium
+ (Charlotte, NC)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>74867</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>167</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>zkH7PTF8</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Audi Field
+ (Washington, DC)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>167</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>UPVAOmVE</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Chase Stadium
  (Fort Lauderdale, FL)</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E6" t="n">
         <v>21550</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0AheRyBg</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Inter Miami</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>UwAwNo2E</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Chicago Fire</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>6gpXy3vi</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>martino gerardo</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>klopas frank</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>167</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1671</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>WdOu5vDd</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Allatin M.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Gillette Stadium
- (Foxborough, MA)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>68756</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>New England Revolution</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>FC Dallas</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>porter caleb</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>luccin peter</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>167</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1671</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>KCHNTNkc</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Unkel T.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Red Bull Arena
- (Harrison, NJ)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>25000</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>New York Red Bulls</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -926,44 +801,24 @@
           <t>FC Cincinnati</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>rJ9D8rzj</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>schwarz sandro</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>roEEsq76</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>noonan pat</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
+      <c r="K6" t="n">
         <v>167</v>
       </c>
-      <c r="P6" t="n">
+      <c r="L6" t="n">
         <v>1671</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
+      <c r="N6" t="n">
         <v>2024</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -972,86 +827,61 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>b3GRSs53</t>
+          <t>8GUEN7pL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dickerson J.
- (Usa)</t>
-        </is>
-      </c>
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Inter&amp;Co Stadium
- (Orlando, FL)</t>
+          <t>Yankee Stadium
+ (New York, NY)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25500</v>
+        <v>54251</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>pareja oscar</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>cushing nicholas</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>167</v>
       </c>
-      <c r="P7" t="n">
+      <c r="L7" t="n">
         <v>1671</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
+      <c r="N7" t="n">
         <v>2024</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1060,18 +890,13 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>tS5WR1K9</t>
+          <t>juKJMRaR</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Penso C.
- (Usa)</t>
-        </is>
-      </c>
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>Subaru Park
@@ -1094,52 +919,32 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>curtin jim</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>63fk89be</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>callaghan brian</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>167</v>
       </c>
-      <c r="P8" t="n">
+      <c r="L8" t="n">
         <v>1671</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
+      <c r="N8" t="n">
         <v>2024</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1148,70 +953,61 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h29zRLZF</t>
+          <t>Usy7kWiL</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45493.89583333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Freemon J.
- (Usa)</t>
-        </is>
-      </c>
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Q2 Stadium
- (Austin, TX)</t>
+          <t>BC Place
+ (Vancouver, BC)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20738</v>
+        <v>54405</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>167</v>
       </c>
-      <c r="P9" t="n">
+      <c r="L9" t="n">
         <v>1671</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
+      <c r="N9" t="n">
         <v>2024</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1220,70 +1016,61 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>QF7rPa4S</t>
+          <t>lSHwpAFr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45493.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Pekmic I.
- (Usa)</t>
-        </is>
-      </c>
+        <v>45528.89583333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Allianz Field
- (Saint Paul, MN)</t>
+          <t>Shell Energy Stadium
+ (Houston, TX)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19400</v>
+        <v>22039</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>167</v>
       </c>
-      <c r="P10" t="n">
+      <c r="L10" t="n">
         <v>1671</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
+      <c r="N10" t="n">
         <v>2024</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1292,142 +1079,124 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nP8vQukM</t>
+          <t>MNAkH5Nl</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45493.89583333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Vazquez R.
- (Usa)</t>
-        </is>
-      </c>
+        <v>45528.89583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>Geodis Park
+ (Nashville, TN)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>167</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>S0BoIo8r</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45528.89583333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Children's Mercy Park
  (Kansas City, KS)</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>21650</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sporting Kansas City</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>167</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>69kBKJCq</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45493.9375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Touchan R.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Dick's Sporting Goods Park
- (Commerce City, CO)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>18061</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>167</v>
       </c>
-      <c r="P12" t="n">
+      <c r="L12" t="n">
         <v>1671</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="n">
+      <c r="N12" t="n">
         <v>2024</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1436,216 +1205,315 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vNmJIcsd</t>
+          <t>0E9gGPxe</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45493.97916666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Chapman A.
- (Usa)</t>
-        </is>
-      </c>
+        <v>45528.9375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>America First Field
+ (Sandy, UT)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>167</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Ik4bFqh1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.97916666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Dignity Health Sports Park
+ (Carson, CA)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>167</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dt32E377</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45528.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Providence Park
+ (Portland, OR)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>167</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vqenBDBt</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45531.875</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Children's Mercy Park
+ (Kansas City, KS)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>167</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1672</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>US Open Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SWX9C8ZI</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45531.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Lumen Field
  (Seattle, WA)</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E17" t="n">
         <v>72000</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Seattle Sounders</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>txUJt9AR</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
+      <c r="K17" t="n">
         <v>167</v>
       </c>
-      <c r="P13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="L17" t="n">
+        <v>1672</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
         <v>2024</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>MHXbihN8</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45493.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bazakos F.
- (Usa)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>BC Place
- (Vancouver, BC)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>54405</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Houston Dynamo</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>167</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>p0lFJwSk</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45493.98958333334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Boiko S.
- (Ukr)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Dignity Health Sports Park
- (Carson, CA)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Los Angeles Galaxy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>167</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>MLS</t>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>US Open Cup</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hQiNHHd2</t>
+          <t>hIoLKAg0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.8125</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Allianz Field
- (Saint Paul, MN)</t>
+          <t>Lower.com Field
+ (Columbus, OH)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19400</v>
+        <v>20371</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -575,41 +575,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>C6QBlj7R</t>
+          <t>KEflYcbt</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Saputo Stadium
- (Montreal, QC)</t>
+          <t>Gillette Stadium
+ (Foxborough, MA)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23112</v>
+        <v>68756</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,41 +638,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dbI3Q902</t>
+          <t>EyfhXHDn</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bank of America Stadium
- (Charlotte, NC)</t>
+          <t>Red Bull Arena
+ (Harrison, NJ)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>74867</v>
+        <v>25000</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York Red Bulls</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>New York Red Bulls</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -701,41 +701,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zkH7PTF8</t>
+          <t>SvbdWyTh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.89583333334</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Audi Field
- (Washington, DC)</t>
+          <t>Soldier Field
+ (Chicago, IL)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20000</v>
+        <v>61500</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>O6hjfSXE</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>DC United</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>FC Dallas</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +764,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UPVAOmVE</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.89583333334</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Chase Stadium
- (Fort Lauderdale, FL)</t>
+          <t>Shell Energy Stadium
+ (Houston, TX)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21550</v>
+        <v>22039</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,41 +827,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8GUEN7pL</t>
+          <t>trWntSE7</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.97916666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Yankee Stadium
- (New York, NY)</t>
+          <t>BC Place
+ (Vancouver, BC)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54251</v>
+        <v>54405</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -884,636 +884,6 @@
       <c r="P7" t="inlineStr">
         <is>
           <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>juKJMRaR</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45528.85416666666</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Subaru Park
- (Chester, PA)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>18500</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Szrwix67</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Philadelphia Union</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Columbus Crew</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>167</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Usy7kWiL</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45528.85416666666</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>BC Place
- (Vancouver, BC)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>54405</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>167</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>lSHwpAFr</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Shell Energy Stadium
- (Houston, TX)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>22039</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Houston Dynamo</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Toronto FC</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>167</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MNAkH5Nl</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Geodis Park
- (Nashville, TN)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Austin FC</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>167</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>S0BoIo8r</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Children's Mercy Park
- (Kansas City, KS)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>21650</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sporting Kansas City</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Orlando City</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>167</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0E9gGPxe</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45528.9375</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>America First Field
- (Sandy, UT)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>20213</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>San Jose Earthquakes</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>167</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ik4bFqh1</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45528.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Dignity Health Sports Park
- (Carson, CA)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Los Angeles Galaxy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>EPngUvhk</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Atlanta Utd</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>167</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dt32E377</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45528.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Providence Park
- (Portland, OR)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>25218</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>167</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vqenBDBt</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45531.875</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Children's Mercy Park
- (Kansas City, KS)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>21650</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sporting Kansas City</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>dtMNCXyk</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Indy Eleven</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>167</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1672</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>US Open Cup</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SWX9C8ZI</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45531.97916666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Lumen Field
- (Seattle, WA)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>167</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1672</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>US Open Cup</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,12 @@
       <c r="B2" s="2" t="n">
         <v>45542.85416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mendoza R.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Lower.com Field
@@ -581,7 +586,12 @@
       <c r="B3" s="2" t="n">
         <v>45542.85416666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ford T.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Gillette Stadium
@@ -644,7 +654,12 @@
       <c r="B4" s="2" t="n">
         <v>45542.85416666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Touchan R.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Red Bull Arena
@@ -707,7 +722,12 @@
       <c r="B5" s="2" t="n">
         <v>45542.89583333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bazakos F.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Soldier Field
@@ -770,7 +790,12 @@
       <c r="B6" s="2" t="n">
         <v>45542.89583333334</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Gonzales G.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Shell Energy Stadium
@@ -833,7 +858,12 @@
       <c r="B7" s="2" t="n">
         <v>45542.97916666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chapman A.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>BC Place
@@ -882,6 +912,825 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Stadium
+ (Atlanta, GA)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>167</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Saputo Stadium
+ (Montreal, QC)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>167</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Audi Field
+ (Washington, DC)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>167</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TQL Stadium
+ (Cincinnati, OH)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>167</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Chase Stadium
+ (Fort Lauderdale, FL)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>21550</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>167</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Inter&amp;Co Stadium
+ (Orlando, FL)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>167</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BMO Field
+ (Toronto, ON)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>167</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xUcLQXdU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Soldier Field
+ (Chicago, IL)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>167</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EkZQoHSu</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Shell Energy Stadium
+ (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>167</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CITYPARK
+ (St. Louis, MO)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>167</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AHSZqech</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45549.9375</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Dick's Sporting Goods Park
+ (Commerce City, CO)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>167</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>l8RwqFCb</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45549.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Dignity Health Sports Park
+ (Carson, CA)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>167</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>foKU4Bi8</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45549.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BC Place
+ (Vancouver, BC)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>167</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>

--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,12 @@
       <c r="B2" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Villarreal A.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Mercedes-Benz Stadium
@@ -581,7 +586,12 @@
       <c r="B3" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Vazquez R.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Saputo Stadium
@@ -644,7 +654,12 @@
       <c r="B4" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Touchan R.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Audi Field
@@ -707,7 +722,12 @@
       <c r="B5" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dickerson J.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>TQL Stadium
@@ -770,7 +790,12 @@
       <c r="B6" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Boiko S.
+ (Ukr)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Chase Stadium
@@ -833,7 +858,12 @@
       <c r="B7" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Penso T.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Inter&amp;Co Stadium
@@ -896,7 +926,12 @@
       <c r="B8" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Penso C.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>BMO Field
@@ -959,7 +994,12 @@
       <c r="B9" s="2" t="n">
         <v>45549.89583333334</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Allatin M.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Soldier Field
@@ -1022,7 +1062,12 @@
       <c r="B10" s="2" t="n">
         <v>45549.89583333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Freemon J.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Shell Energy Stadium
@@ -1085,7 +1130,12 @@
       <c r="B11" s="2" t="n">
         <v>45549.89583333334</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>De Oliveira M.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>CITYPARK
@@ -1148,7 +1198,12 @@
       <c r="B12" s="2" t="n">
         <v>45549.9375</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dujic F.
+ (Can)</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Dick's Sporting Goods Park
@@ -1211,7 +1266,12 @@
       <c r="B13" s="2" t="n">
         <v>45549.97916666666</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Unkel T.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>Dignity Health Sports Park
@@ -1274,7 +1334,12 @@
       <c r="B14" s="2" t="n">
         <v>45549.97916666666</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Szpala L.
+ (Usa)</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>BC Place
@@ -1337,7 +1402,12 @@
       <c r="B15" s="2" t="n">
         <v>45550.84375</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Fischer D.
+ (Can)</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Lumen Field
@@ -1386,825 +1456,6 @@
         </is>
       </c>
       <c r="P15" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dYUosgsB</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz Stadium
- (Atlanta, GA)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>71000</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>EPngUvhk</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Atlanta Utd</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0AheRyBg</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Inter Miami</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>167</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>U3Cs29yR</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Gillette Stadium
- (Foxborough, MA)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>68756</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>New England Revolution</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>CF Montreal</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>167</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>vcKjtDdH</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Yankee Stadium
- (New York, NY)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>54251</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Szrwix67</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Philadelphia Union</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>167</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Me49cTqr</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>BMO Field
- (Toronto, ON)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>30991</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Toronto FC</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Columbus Crew</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>167</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>ImJfuXBN</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45553.88541666666</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Inter&amp;Co Stadium
- (Orlando, FL)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>25500</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Orlando City</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>QJF7WTFB</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>167</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>0n3Ddmal</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Shell Energy Stadium
- (Houston, TX)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>22039</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Houston Dynamo</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>167</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SM4QZAZp</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Allianz Field
- (Saint Paul, MN)</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>19400</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>zXFxsw2a</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Minnesota United</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>FC Cincinnati</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>167</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>URr9bfCo</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Geodis Park
- (Nashville, TN)</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>UwAwNo2E</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Chicago Fire</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>167</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>QDIbviRT</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Children's Mercy Park
- (Kansas City, KS)</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>21650</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sporting Kansas City</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>167</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rVnDcERi</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45553.9375</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>America First Field
- (Sandy, UT)</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>20213</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>FC Dallas</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>167</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xhnHdYtb</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>BMO Stadium
- (Los Angeles, CA)</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>22000</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Austin FC</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>167</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>GroLehd4</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Providence Park
- (Portland, OR)</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>25218</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Los Angeles Galaxy</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>167</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YJuQfCBA</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Lumen Field
- (Seattle, WA)</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>San Jose Earthquakes</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>167</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>

--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Villarreal A.
+          <t>Freemon J.
  (Usa)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Stadium
- (Atlanta, GA)</t>
+          <t>Yankee Stadium
+ (New York, NY)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71000</v>
+        <v>54251</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Atlanta Utd</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>6XwYhjtN</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.70833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vazquez R.
+          <t>Allatin M.
  (Usa)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Saputo Stadium
- (Montreal, QC)</t>
+          <t>Bank of America Stadium
+ (Charlotte, NC)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23112</v>
+        <v>74867</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>rBhIe7Ef</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Touchan R.
+          <t>Szpala L.
  (Usa)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Audi Field
- (Washington, DC)</t>
+          <t>Saputo Stadium
+ (Montreal, QC)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20000</v>
+        <v>23112</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>CF Montreal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dickerson J.
- (Usa)</t>
+          <t>Boiko S.
+ (Ukr)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TQL Stadium
- (Cincinnati, OH)</t>
+          <t>Lower.com Field
+ (Columbus, OH)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26000</v>
+        <v>20371</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boiko S.
- (Ukr)</t>
+          <t>Penso C.
+ (Usa)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Chase Stadium
- (Fort Lauderdale, FL)</t>
+          <t>Red Bull Arena
+ (Harrison, NJ)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21550</v>
+        <v>25000</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York Red Bulls</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Atlanta Utd</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -852,46 +852,46 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>2uJ8nlJj</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Penso T.
+          <t>Rivas V.
  (Usa)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Inter&amp;Co Stadium
- (Orlando, FL)</t>
+          <t>Q2 Stadium
+ (Austin, TX)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25500</v>
+        <v>20738</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -920,46 +920,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Penso C.
+          <t>Da Silva A.
  (Usa)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BMO Field
- (Toronto, ON)</t>
+          <t>Toyota Stadium
+ (Frisco, TX)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30991</v>
+        <v>20500</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Toronto FC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -988,46 +988,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allatin M.
- (Usa)</t>
+          <t>Lauziere P.
+ (Can)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Soldier Field
- (Chicago, IL)</t>
+          <t>Geodis Park
+ (Nashville, TN)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>61500</v>
+        <v>30000</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>New York Red Bulls</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1056,46 +1056,46 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Freemon J.
+          <t>Pekmic I.
  (Usa)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Shell Energy Stadium
- (Houston, TX)</t>
+          <t>Children's Mercy Park
+ (Kansas City, KS)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22039</v>
+        <v>21650</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1124,46 +1124,46 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>tdBLfRT0</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>De Oliveira M.
+          <t>Mendoza R.
  (Usa)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CITYPARK
- (St. Louis, MO)</t>
+          <t>Dick's Sporting Goods Park
+ (Commerce City, CO)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22423</v>
+        <v>18061</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Toronto FC</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1192,36 +1192,36 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45549.9375</v>
+        <v>45556.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dujic F.
- (Can)</t>
+          <t>Penso T.
+ (Usa)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dick's Sporting Goods Park
- (Commerce City, CO)</t>
+          <t>America First Field
+ (Sandy, UT)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>18061</v>
+        <v>20213</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1260,15 +1260,15 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45556.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unkel T.
+          <t>Marrufo J.
  (Usa)</t>
         </is>
       </c>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1328,46 +1328,46 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45556.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Szpala L.
- (Usa)</t>
+          <t>Montero R.
+ (Cos)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BC Place
- (Vancouver, BC)</t>
+          <t>PayPal Park
+ (San Jose, CA)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>54405</v>
+        <v>18000</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>San Jose Earthquakes</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1388,74 +1388,6 @@
         </is>
       </c>
       <c r="P14" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rVQsrZR4</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45550.84375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Fischer D.
- (Can)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Lumen Field
- (Seattle, WA)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Sporting Kansas City</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>167</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>

--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,30 +480,50 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
@@ -512,66 +532,86 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
+          <t>YuZ4CywD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45556.625</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Freemon J.
+          <t>Pekmic I.
  (Usa)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yankee Stadium
- (New York, NY)</t>
+          <t>Mercedes-Benz Stadium
+ (Atlanta, GA)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54251</v>
+        <v>71000</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Atlanta Utd</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>valentino rob</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>schwarz sandro</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>167</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>1671</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="R2" t="n">
         <v>2024</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -580,15 +620,15 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
+          <t>UuWb8pb0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45556.70833333334</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allatin M.
+          <t>Rivas V.
  (Usa)</t>
         </is>
       </c>
@@ -614,32 +654,52 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>smith dean</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>courtois laurent</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>167</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>1671</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
         <v>2024</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -648,66 +708,86 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rBhIe7Ef</t>
+          <t>llHizuVJ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Szpala L.
+          <t>Chapman A.
  (Usa)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Saputo Stadium
- (Montreal, QC)</t>
+          <t>Lower.com Field
+ (Columbus, OH)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>23112</v>
+        <v>20371</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>nancy wilfried</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>curtin jim</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>167</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>1671</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>2024</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -716,36 +796,36 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
+          <t>CWX8BehJ</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boiko S.
- (Ukr)</t>
+          <t>Dujic F.
+ (Can)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lower.com Field
- (Columbus, OH)</t>
+          <t>TQL Stadium
+ (Cincinnati, OH)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20371</v>
+        <v>26000</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -758,24 +838,44 @@
           <t>Orlando City</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>noonan pat</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>pareja oscar</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>167</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>1671</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="R5" t="n">
         <v>2024</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -784,66 +884,86 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
+          <t>pK2NUIhs</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Penso C.
+          <t>Da Silva A.
  (Usa)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Red Bull Arena
- (Harrison, NJ)</t>
+          <t>Gillette Stadium
+ (Foxborough, MA)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25000</v>
+        <v>68756</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>New York Red Bulls</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Atlanta Utd</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>porter caleb</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>lesesne troy</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>167</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>1671</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="R6" t="n">
         <v>2024</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -852,66 +972,86 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
+          <t>MFWf9Qrf</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rivas V.
+          <t>Touchan R.
  (Usa)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q2 Stadium
- (Austin, TX)</t>
+          <t>BC Place
+ (Vancouver, BC)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20738</v>
+        <v>54405</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>sartini vanni</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ramsay eric</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>167</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>1671</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="R7" t="n">
         <v>2024</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -920,36 +1060,36 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
+          <t>r5LQTx8m</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Da Silva A.
+          <t>De Oliveira M.
  (Usa)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Toyota Stadium
- (Frisco, TX)</t>
+          <t>Children's Mercy Park
+ (Kansas City, KS)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20500</v>
+        <v>21650</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -962,24 +1102,28 @@
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>167</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>1671</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
         <v>2024</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -988,66 +1132,70 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
+          <t>QTAVSdNg</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lauziere P.
- (Can)</t>
+          <t>Penso T.
+ (Usa)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Geodis Park
- (Nashville, TN)</t>
+          <t>CITYPARK
+ (St. Louis, MO)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30000</v>
+        <v>22423</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>167</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>1671</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
+      <c r="R9" t="n">
         <v>2024</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1056,66 +1204,70 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
+          <t>4K9ZRGx0</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.9375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pekmic I.
+          <t>Ford T.
  (Usa)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Children's Mercy Park
- (Kansas City, KS)</t>
+          <t>Dick's Sporting Goods Park
+ (Commerce City, CO)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21650</v>
+        <v>18061</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sporting Kansas City</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
         <v>167</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>1671</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
+      <c r="R10" t="n">
         <v>2024</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1124,66 +1276,70 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>YgEwRzh6</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45556.9375</v>
+        <v>45570.97916666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mendoza R.
+          <t>Unkel T.
  (Usa)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dick's Sporting Goods Park
- (Commerce City, CO)</t>
+          <t>Dignity Health Sports Park
+ (Carson, CA)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18061</v>
+        <v>27000</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles Galaxy</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Toronto FC</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
         <v>167</v>
       </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
         <v>1671</v>
       </c>
-      <c r="M11" t="n">
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
         <v>2024</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1192,66 +1348,70 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
+          <t>CpDsQf7C</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45556.9375</v>
+        <v>45570.97916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Penso T.
+          <t>Allatin M.
  (Usa)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>America First Field
- (Sandy, UT)</t>
+          <t>PayPal Park
+ (San Jose, CA)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20213</v>
+        <v>18000</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Real Salt Lake</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
         <v>167</v>
       </c>
-      <c r="L12" t="n">
+      <c r="P12" t="n">
         <v>1671</v>
       </c>
-      <c r="M12" t="n">
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
+      <c r="R12" t="n">
         <v>2024</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1260,66 +1420,70 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
+          <t>SvGeZbpQ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45571.70833333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Marrufo J.
- (Usa)</t>
+          <t>Boiko S.
+ (Ukr)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dignity Health Sports Park
- (Carson, CA)</t>
+          <t>Yankee Stadium
+ (New York, NY)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>27000</v>
+        <v>54251</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Los Angeles Galaxy</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
         <v>167</v>
       </c>
-      <c r="L13" t="n">
+      <c r="P13" t="n">
         <v>1671</v>
       </c>
-      <c r="M13" t="n">
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
+      <c r="R13" t="n">
         <v>2024</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
@@ -1328,66 +1492,70 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
+          <t>f92nPEMI</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45571.83333333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montero R.
- (Cos)</t>
+          <t>Villarreal A.
+ (Usa)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PayPal Park
- (San Jose, CA)</t>
+          <t>Providence Park
+ (Portland, OR)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18000</v>
+        <v>25218</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
         <v>167</v>
       </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>1671</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
+      <c r="R14" t="n">
         <v>2024</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
